--- a/artfynd/A 44382-2023 artfynd.xlsx
+++ b/artfynd/A 44382-2023 artfynd.xlsx
@@ -1247,7 +1247,7 @@
         <v>133850883</v>
       </c>
       <c r="B7" t="n">
-        <v>80475</v>
+        <v>80482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 44382-2023 artfynd.xlsx
+++ b/artfynd/A 44382-2023 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115413306</v>
+        <v>133850883</v>
       </c>
       <c r="B2" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hidberget, Ås lm</t>
+          <t>Skogen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574990</v>
+        <v>575048</v>
       </c>
       <c r="R2" t="n">
-        <v>7205860</v>
+        <v>7205842</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:04</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:04</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,71 +765,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115413296</v>
+        <v>115417725</v>
       </c>
       <c r="B3" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hidberget, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574968</v>
+        <v>574989</v>
       </c>
       <c r="R3" t="n">
-        <v>7205766</v>
+        <v>7205857</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,7 +847,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +857,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,37 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115417680</v>
+        <v>115417726</v>
       </c>
       <c r="B4" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574940</v>
+        <v>574942</v>
       </c>
       <c r="R4" t="n">
-        <v>7205874</v>
+        <v>7205870</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1020,15 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115417726</v>
+        <v>115417680</v>
       </c>
       <c r="B5" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574942</v>
+        <v>574940</v>
       </c>
       <c r="R5" t="n">
-        <v>7205870</v>
+        <v>7205874</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1132,37 +1098,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115417725</v>
+        <v>115413306</v>
       </c>
       <c r="B6" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>574989</v>
+        <v>574990</v>
       </c>
       <c r="R6" t="n">
-        <v>7205857</v>
+        <v>7205860</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1244,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133850883</v>
+        <v>115413296</v>
       </c>
       <c r="B7" t="n">
-        <v>80482</v>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,37 +1216,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skogen, Ås lm</t>
+          <t>Hidberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575048</v>
+        <v>574968</v>
       </c>
       <c r="R7" t="n">
-        <v>7205842</v>
+        <v>7205766</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,17 +1279,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-43</t>
+          <t>2024-03-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,12 +1309,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
